--- a/construction_template/data/templates_blank/daily_log_1.xlsx
+++ b/construction_template/data/templates_blank/daily_log_1.xlsx
@@ -5,7 +5,6 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EmsSuperAllSrc\EmsSupervision\xlt\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3DA49C-45C2-47A4-BBBF-56038D5076AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -22,7 +21,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
-    <t>任泰技術顧問有限公司</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t>第一聯</t>
@@ -34,7 +33,7 @@
     <t>本日天氣:上午</t>
   </si>
   <si>
-    <t>晴天</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t>下午</t>
@@ -46,25 +45,25 @@
     <t>工程名稱</t>
   </si>
   <si>
-    <t>111年度西區水利建造物檢修改善及災後淤土、樹木復原及設施搶修預約維護工程</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t>契約編號</t>
   </si>
   <si>
-    <t>H-111-03-111040</t>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t>主辦機關</t>
   </si>
   <si>
-    <t>臺北市政府工務局水利工程處</t>
-  </si>
-  <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <r>
       <t>契約工期</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <b/>
         <sz val="8"/>
@@ -74,16 +73,16 @@
       </rPr>
       <t>(註3)</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>開工日期</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>預定竣工日期</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <b/>
         <sz val="10"/>
@@ -98,10 +97,10 @@
     <t>實際竣工日期</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>契約變更次數</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <b/>
         <sz val="10"/>
@@ -111,7 +110,7 @@
       </rPr>
       <t>(註4)</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>工期展延天數</t>
@@ -123,10 +122,10 @@
     <t>原契約：</t>
   </si>
   <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <t>預定進度(%)</t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <b/>
         <sz val="10"/>
@@ -136,14 +135,14 @@
       </rPr>
       <t>(註5)</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">實際進度(%)
 </t>
     </r>
-    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <r>
       <rPr>
         <b/>
         <sz val="10"/>
@@ -153,7 +152,7 @@
       </rPr>
       <t>(註5)</t>
     </r>
-    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>變更後契約：</t>

--- a/construction_template/data/templates_blank/daily_log_1.xlsx
+++ b/construction_template/data/templates_blank/daily_log_1.xlsx
@@ -5,6 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url=""/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3DA49C-45C2-47A4-BBBF-56038D5076AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -21,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t>第一聯</t>
@@ -33,7 +34,7 @@
     <t>本日天氣:上午</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t>下午</t>
@@ -45,25 +46,25 @@
     <t>工程名稱</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t>契約編號</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t/>
   </si>
   <si>
     <t>主辦機關</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <r>
+    <t/>
+  </si>
+  <si>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>契約工期</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <b/>
         <sz val="8"/>
@@ -73,16 +74,16 @@
       </rPr>
       <t>(註3)</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>開工日期</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>預定竣工日期</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <b/>
         <sz val="10"/>
@@ -97,10 +98,10 @@
     <t>實際竣工日期</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>契約變更次數</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <b/>
         <sz val="10"/>
@@ -110,7 +111,7 @@
       </rPr>
       <t>(註4)</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>工期展延天數</t>
@@ -122,10 +123,10 @@
     <t>原契約：</t>
   </si>
   <si>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t>預定進度(%)</t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <b/>
         <sz val="10"/>
@@ -135,14 +136,14 @@
       </rPr>
       <t>(註5)</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <t xml:space="preserve">實際進度(%)
 </t>
     </r>
-    <r>
+    <r xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
       <rPr>
         <b/>
         <sz val="10"/>
@@ -152,7 +153,7 @@
       </rPr>
       <t>(註5)</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>變更後契約：</t>
@@ -1650,7 +1651,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A3:L44"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>

--- a/construction_template/data/templates_blank/daily_log_1.xlsx
+++ b/construction_template/data/templates_blank/daily_log_1.xlsx
@@ -162,7 +162,7 @@
     <t>一、工程進行情況（含約定之重要施工項目及數量）：</t>
   </si>
   <si>
-    <t>本日重要工作：1.假日自行車多，無施工。</t>
+    <t>本日重要工作：</t>
   </si>
   <si>
     <t>二、監督依設計圖說及核定施工圖說施工（含約定之檢驗停留點及施工抽查等情形）：</t>
